--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_influence/lang_influence__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_influence/lang_influence__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Random Forces.</t>
+          <t>Lực lượng ngẫu nhiên</t>
         </is>
       </c>
     </row>
@@ -705,8 +705,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hiệp hội Tiên phong được thành lập sau Chiến tranh Wuthering bởi cộng đồng loài người. Đôi khi họ được gọi tắt là PA.
-Do mối quan hệ tin tưởng giữa Resonators và người dân thường ở Huanglong, PA có quy mô tương đối lớn ở Huanglong và đảm nhận nhiều trách nhiệm hơn. Gia nhập PA là điều đáng tự hào ở Huanglong.</t>
+          <t>Hiệp Hội Tiên Phong được thành lập sau Chiến Tranh Gió Hú bởi cộng đồng loài người. Họ thường được gọi tắt là PA.
+Nhờ mối quan hệ tin tưởng giữa Resonator và người dân thường tại Huanglong, PA đã phát triển quy mô khá lớn ở đây và đảm nhận nhiều trách nhiệm hơn. Gia nhập PA là điều đáng tự hào tại Huanglong.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chi nhánh Huanglong</t>
+          <t>Chi Nhánh Huanglong</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Squeak Express</t>
+          <t>Tàu Squeak Tốc Hành</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Một công ty vận tải hoạt động trên toàn thế giới. Họ sẵn sàng nhận những nhiệm vụ vận chuyển nguy hiểm nhất và được nhiều thế lực tin tưởng. Với niềm tin "Hòa bình mang lại thịnh vượng", họ luôn tránh mọi tình huống xung đột.</t>
+          <t>Một công ty vận tải hoạt động trên toàn thế giới. Họ sẵn sàng đảm nhận những nhiệm vụ vận chuyển nguy hiểm nhất và được nhiều thế lực tin tưởng. Với niềm tin "Hòa bình mang lại thịnh vượng", họ luôn tránh mọi tình huống xung đột.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Chi nhánh Huanglong</t>
+          <t>Chi Nhánh Huanglong</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The Sea Drake.</t>
+          <t>Rồng Biển.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Họ tụ tập tại Xưởng Sửa Chữa Rắn, là một nhóm những người đam mê sáng chế đến từ khắp nơi ở Huanglong. Họ tự gọi mình là Hải Xà. Dù tất cả đều đang cố gắng kêu gọi đầu tư, mọi chuyện luôn trở nên tồi tệ với họ.</t>
+          <t>Họ tụ tập tại Xưởng Sửa Chữa Rắn, là một nhóm những người đam mê phát minh đến từ nhiều nơi ở Huanglong. Họ tự gọi mình là Hải Xà. Dù ai cũng cố gắng kêu gọi đầu tư, nhưng mọi chuyện luôn đổ bể.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The Piggy.</t>
+          <t>Chú Lợn Con</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Exile là tên gọi chung cho những cá nhân và tổ chức bị trục xuất khỏi thành phố, phạm tội và sống bằng nghề nhặt phế liệu. Họ không tuân theo bất kỳ quyền hạn pháp lý nào. Những cá nhân mạnh nhất trong mỗi băng nhóm sẽ có quyền ra lệnh. Tại Huanglong, họ tụ tập ở Thành Phố Hoang Phế. Họ bị chia thành 2 phe do khác biệt về niềm tin. Một trong những băng nhóm này khá thân thiện với người ngoài.</t>
+          <t>"Kẻ Lưu Đày" là danh xưng dành cho tất cả cá nhân và tổ chức bị trục xuất khỏi thành phố, phạm tội và kiếm sống bằng nghề nhặt rác. Chúng không chịu sự quản thúc của bất kỳ pháp luật nào. Những cá nhân mạnh nhất trong mỗi băng nhóm sẽ có quyền ra lệnh. Tại Huanglong, chúng tụ tập ở Wasted Metropolis. Chúng chia thành 2 phe phái khác nhau do bất đồng về niềm tin. Một trong những băng đảng này có vẻ khá thân thiện với người ngoài.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Một hội bí mật lang thang khắp thế giới. Các thành viên của họ chỉ khao khát quyền lực và sự tiến hóa, và tất cả đều mang ngoại hình kỳ lạ. Nhiều thông tin về họ vẫn đang chờ được tiết lộ.</t>
+          <t>Một hội kín lang thang khắp thế giới. Các thành viên của họ chỉ khao khát quyền lực và sự tiến hóa, và đều mang ngoại hình kỳ lạ. Nhiều thông tin về họ vẫn đang chờ được tiết lộ.</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Một tổ chức bí mật thề cứu thế giới dưới danh nghĩa Bờ Đen. Họ mạo hiểm đến những nơi nguy hiểm nhất và tập hợp đồng minh có cùng ý chí cứu thế. Các thành viên và khách mời của họ đều mang một bông hoa đen như biểu tượng.</t>
+          <t>Một tổ chức bí mật thề cứu thế giới dưới danh nghĩa Black Shore. Họ dấn thân vào những nơi nguy hiểm nhất và tập hợp đồng minh cùng chí hướng để cứu thế giới. Các thành viên và khách mời của họ đều mang theo một bông hoa đen như biểu tượng.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Quốc gia Ngẫu nhiên</t>
+          <t>Quốc gia ngẫu nhiên</t>
         </is>
       </c>
     </row>
@@ -1682,8 +1682,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Huanglong là một quốc gia với hàng ngàn năm lịch sử. Lịch sử lâu đời đã hun đúc nên một nền văn hóa đặc sắc và truyền thống cho dân tộc này. Mặc dù Vết Nứt Than Thở đã làm gián đoạn sự phát triển của nó, nhưng người dân nơi đây vẫn không ngừng chiến đấu và cố gắng kế thừa những gì còn sót lại của quốc gia.
-Trong Kỷ Nguyên Phục Hưng, ngành công nghiệp Tacetite của Huanglong đã mang lại sức sống mới cho đất nước này. Với những đơn hàng Tacetite không ngừng nghỉ, nền kinh tế Huanglong chưa bao giờ ngừng phát triển.</t>
+          <t>Huanglong là một quốc gia với lịch sử hàng nghìn năm. Lịch sử lâu đời đã hun đúc nên một nền văn hóa đặc sắc và truyền thống cho dân tộc này. Dù Vết Nứt Than Thở đã làm gián đoạn sự phát triển, nhưng người dân nơi đây vẫn kiên cường chiến đấu và nỗ lực kế thừa những gì còn sót lại của quốc gia.
+Trong Kỷ Nguyên Phục Hồi, ngành công nghiệp Tacetite của Huanglong đã thổi luồng sinh khí mới vào đất nước. Với nhu cầu không ngừng về Tacetite, nền kinh tế Huanglong chưa bao giờ ngừng bùng nổ.</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tổ chức Không Biên Giới</t>
+          <t>Tổ Chức Không Biên Giới</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Không thuộc quyền quản lý của bất kỳ ai, họ hành động theo ý chí và quy tắc riêng. Chúng ta cần xử lý những kẻ nguy hiểm một cách cẩn thận, đề phòng tình hình trở nên tồi tệ.</t>
+          <t>Không thuộc quyền quản lý của ai, chúng tự do hành động theo ý chí và luật lệ riêng. Ta cần xử lý những kẻ nguy hiểm một cách cẩn trọng, đề phòng tình hình trở nên tồi tệ.</t>
         </is>
       </c>
     </row>
